--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_11/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_11/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>74.84</v>
+        <v>76.41</v>
       </c>
       <c r="D2" t="n">
-        <v>13.62</v>
+        <v>12.49</v>
       </c>
       <c r="E2" t="n">
-        <v>18.2</v>
+        <v>16.35</v>
       </c>
       <c r="F2" t="n">
-        <v>57.56</v>
+        <v>60.13</v>
       </c>
       <c r="G2" t="n">
-        <v>63.03</v>
+        <v>66.45</v>
       </c>
       <c r="H2" t="n">
-        <v>71.77</v>
+        <v>73.94</v>
       </c>
       <c r="I2" t="n">
-        <v>85.84999999999999</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>42.44</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>47.51</v>
+        <v>44.18</v>
       </c>
       <c r="D3" t="n">
-        <v>0.51</v>
+        <v>5.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1.08</v>
+        <v>12.22</v>
       </c>
       <c r="F3" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="G3" t="n">
         <v>45.51</v>
       </c>
-      <c r="G3" t="n">
-        <v>47.67</v>
-      </c>
       <c r="H3" t="n">
-        <v>47.68</v>
+        <v>45.52</v>
       </c>
       <c r="I3" t="n">
-        <v>47.68</v>
+        <v>45.53</v>
       </c>
       <c r="J3" t="n">
-        <v>48.17</v>
+        <v>46.27</v>
       </c>
       <c r="K3" t="n">
-        <v>2.66</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>9.369999999999999</v>
+        <v>7.39</v>
       </c>
       <c r="D4" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="E4" t="n">
-        <v>25.17</v>
+        <v>27.53</v>
       </c>
       <c r="F4" t="n">
-        <v>6.01</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>7.54</v>
+        <v>5.64</v>
       </c>
       <c r="H4" t="n">
-        <v>8.49</v>
+        <v>6.66</v>
       </c>
       <c r="I4" t="n">
-        <v>11.18</v>
+        <v>8.08</v>
       </c>
       <c r="J4" t="n">
-        <v>13.34</v>
+        <v>10.83</v>
       </c>
       <c r="K4" t="n">
-        <v>7.33</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>80.69</v>
+        <v>47.37</v>
       </c>
       <c r="D5" t="n">
-        <v>28.65</v>
+        <v>8.07</v>
       </c>
       <c r="E5" t="n">
-        <v>35.51</v>
+        <v>17.03</v>
       </c>
       <c r="F5" t="n">
-        <v>51.76</v>
+        <v>30.62</v>
       </c>
       <c r="G5" t="n">
-        <v>61.75</v>
+        <v>41.65</v>
       </c>
       <c r="H5" t="n">
-        <v>75.25</v>
+        <v>48.74</v>
       </c>
       <c r="I5" t="n">
-        <v>82.79000000000001</v>
+        <v>52.19</v>
       </c>
       <c r="J5" t="n">
-        <v>181.2</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>129.44</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>2.48</v>
+        <v>4.45</v>
       </c>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>18.01</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>2.01</v>
+        <v>3.76</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>4.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.38</v>
+        <v>4.47</v>
       </c>
       <c r="I6" t="n">
-        <v>2.56</v>
+        <v>4.78</v>
       </c>
       <c r="J6" t="n">
-        <v>3.74</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
